--- a/database/event/8049/event_8049_evp_summary.xlsx
+++ b/database/event/8049/event_8049_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8049" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8049" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>4.0969</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7912</v>
+        <v>4.247</v>
       </c>
       <c r="E2" t="n">
         <v>11.5559</v>
@@ -548,7 +548,7 @@
         <v>3.046</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6944</v>
+        <v>3.0495</v>
       </c>
       <c r="E3" t="n">
         <v>8.5916</v>
@@ -594,7 +594,7 @@
         <v>2.9011</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5431</v>
+        <v>2.8843</v>
       </c>
       <c r="E4" t="n">
         <v>8.1828</v>
@@ -640,7 +640,7 @@
         <v>2.7859</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4229</v>
+        <v>2.7531</v>
       </c>
       <c r="E5" t="n">
         <v>7.8579</v>
@@ -686,7 +686,7 @@
         <v>2.6848</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3174</v>
+        <v>2.6379</v>
       </c>
       <c r="E6" t="n">
         <v>7.5728</v>
@@ -732,7 +732,7 @@
         <v>2.2241</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8367</v>
+        <v>2.113</v>
       </c>
       <c r="E7" t="n">
         <v>6.2734</v>
@@ -778,7 +778,7 @@
         <v>1.8948</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4929</v>
+        <v>1.7377</v>
       </c>
       <c r="E8" t="n">
         <v>5.3444</v>
@@ -824,7 +824,7 @@
         <v>1.8242</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4193</v>
+        <v>1.6573</v>
       </c>
       <c r="E9" t="n">
         <v>5.1455</v>
@@ -870,7 +870,7 @@
         <v>1.8143</v>
       </c>
       <c r="D10" t="n">
-        <v>1.409</v>
+        <v>1.646</v>
       </c>
       <c r="E10" t="n">
         <v>5.1175</v>
@@ -916,7 +916,7 @@
         <v>1.8125</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4071</v>
+        <v>1.644</v>
       </c>
       <c r="E11" t="n">
         <v>5.1125</v>
@@ -962,7 +962,7 @@
         <v>1.5896</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1745</v>
+        <v>1.39</v>
       </c>
       <c r="E12" t="n">
         <v>4.4837</v>
@@ -1008,7 +1008,7 @@
         <v>1.5197</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1015</v>
+        <v>1.3103</v>
       </c>
       <c r="E13" t="n">
         <v>4.2866</v>
@@ -1054,7 +1054,7 @@
         <v>1.3874</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9634</v>
+        <v>1.1596</v>
       </c>
       <c r="E14" t="n">
         <v>3.9134</v>
@@ -1100,7 +1100,7 @@
         <v>1.2657</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8364</v>
+        <v>1.0208</v>
       </c>
       <c r="E15" t="n">
         <v>3.57</v>
@@ -1146,7 +1146,7 @@
         <v>1.2566</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8269</v>
+        <v>1.0105</v>
       </c>
       <c r="E16" t="n">
         <v>3.5444</v>
@@ -1192,7 +1192,7 @@
         <v>1.2271</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7962</v>
+        <v>0.9769</v>
       </c>
       <c r="E17" t="n">
         <v>3.4613</v>
@@ -1238,7 +1238,7 @@
         <v>1.1369</v>
       </c>
       <c r="D18" t="n">
-        <v>0.702</v>
+        <v>0.8741</v>
       </c>
       <c r="E18" t="n">
         <v>3.2068</v>
@@ -1284,7 +1284,7 @@
         <v>0.9409</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4974</v>
+        <v>0.6508</v>
       </c>
       <c r="E19" t="n">
         <v>2.6539</v>
@@ -1330,7 +1330,7 @@
         <v>0.929</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4851</v>
+        <v>0.6373</v>
       </c>
       <c r="E20" t="n">
         <v>2.6205</v>
@@ -1376,7 +1376,7 @@
         <v>0.9173</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4728</v>
+        <v>0.6239</v>
       </c>
       <c r="E21" t="n">
         <v>2.5874</v>
@@ -1422,7 +1422,7 @@
         <v>0.8206</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3719</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>2.3145</v>
@@ -1468,7 +1468,7 @@
         <v>0.7816</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3312</v>
+        <v>0.4692</v>
       </c>
       <c r="E23" t="n">
         <v>2.2045</v>
@@ -1514,7 +1514,7 @@
         <v>0.7517</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3</v>
+        <v>0.4352</v>
       </c>
       <c r="E24" t="n">
         <v>2.1204</v>
@@ -1560,7 +1560,7 @@
         <v>0.7127</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2593</v>
+        <v>0.3908</v>
       </c>
       <c r="E25" t="n">
         <v>2.0104</v>
@@ -1606,7 +1606,7 @@
         <v>0.6932</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2389</v>
+        <v>0.3685</v>
       </c>
       <c r="E26" t="n">
         <v>1.9552</v>
@@ -1652,7 +1652,7 @@
         <v>0.68</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2251</v>
+        <v>0.3534</v>
       </c>
       <c r="E27" t="n">
         <v>1.9179</v>
@@ -1698,7 +1698,7 @@
         <v>0.6718</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2166</v>
+        <v>0.3441</v>
       </c>
       <c r="E28" t="n">
         <v>1.8949</v>
@@ -1744,7 +1744,7 @@
         <v>0.6667</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2113</v>
+        <v>0.3383</v>
       </c>
       <c r="E29" t="n">
         <v>1.8805</v>
@@ -1790,7 +1790,7 @@
         <v>0.6637999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2083</v>
+        <v>0.335</v>
       </c>
       <c r="E30" t="n">
         <v>1.8724</v>
@@ -1836,7 +1836,7 @@
         <v>0.654</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1981</v>
+        <v>0.3239</v>
       </c>
       <c r="E31" t="n">
         <v>1.8448</v>
@@ -1882,7 +1882,7 @@
         <v>0.6512</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1951</v>
+        <v>0.3207</v>
       </c>
       <c r="E32" t="n">
         <v>1.8369</v>
@@ -1928,7 +1928,7 @@
         <v>0.6228</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1654</v>
+        <v>0.2883</v>
       </c>
       <c r="E33" t="n">
         <v>1.7566</v>
@@ -1974,7 +1974,7 @@
         <v>0.5985</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1401</v>
+        <v>0.2606</v>
       </c>
       <c r="E34" t="n">
         <v>1.6881</v>
@@ -2020,7 +2020,7 @@
         <v>0.57</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1104</v>
+        <v>0.2282</v>
       </c>
       <c r="E35" t="n">
         <v>1.6079</v>
@@ -2066,7 +2066,7 @@
         <v>0.5628</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1028</v>
+        <v>0.2199</v>
       </c>
       <c r="E36" t="n">
         <v>1.5874</v>
@@ -2112,7 +2112,7 @@
         <v>0.5518999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0915</v>
+        <v>0.2076</v>
       </c>
       <c r="E37" t="n">
         <v>1.5568</v>
@@ -2158,7 +2158,7 @@
         <v>0.5441</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0833</v>
+        <v>0.1986</v>
       </c>
       <c r="E38" t="n">
         <v>1.5347</v>
@@ -2204,7 +2204,7 @@
         <v>0.532</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0707</v>
+        <v>0.1848</v>
       </c>
       <c r="E39" t="n">
         <v>1.5005</v>
@@ -2250,7 +2250,7 @@
         <v>0.4752</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0114</v>
+        <v>0.1201</v>
       </c>
       <c r="E40" t="n">
         <v>1.3403</v>
@@ -2296,7 +2296,7 @@
         <v>0.4482</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0168</v>
+        <v>0.0893</v>
       </c>
       <c r="E41" t="n">
         <v>1.2641</v>
@@ -2342,7 +2342,7 @@
         <v>0.4064</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0604</v>
+        <v>0.0417</v>
       </c>
       <c r="E42" t="n">
         <v>1.1462</v>
@@ -2388,7 +2388,7 @@
         <v>0.3819</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.0138</v>
       </c>
       <c r="E43" t="n">
         <v>1.0771</v>
@@ -2434,7 +2434,7 @@
         <v>0.3262</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1441</v>
+        <v>-0.0497</v>
       </c>
       <c r="E44" t="n">
         <v>0.92</v>
@@ -2480,7 +2480,7 @@
         <v>0.2831</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1891</v>
+        <v>-0.0988</v>
       </c>
       <c r="E45" t="n">
         <v>0.7985</v>
@@ -2526,7 +2526,7 @@
         <v>0.2824</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1898</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="E46" t="n">
         <v>0.7966</v>
@@ -2572,7 +2572,7 @@
         <v>0.2635</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2096</v>
+        <v>-0.1212</v>
       </c>
       <c r="E47" t="n">
         <v>0.7431</v>
@@ -2618,7 +2618,7 @@
         <v>0.2202</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2547</v>
+        <v>-0.1705</v>
       </c>
       <c r="E48" t="n">
         <v>0.621</v>
@@ -2664,7 +2664,7 @@
         <v>0.2184</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2566</v>
+        <v>-0.1725</v>
       </c>
       <c r="E49" t="n">
         <v>0.616</v>
@@ -2710,7 +2710,7 @@
         <v>0.1924</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2838</v>
+        <v>-0.2022</v>
       </c>
       <c r="E50" t="n">
         <v>0.5426</v>
@@ -2756,7 +2756,7 @@
         <v>0.1165</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3629</v>
+        <v>-0.2886</v>
       </c>
       <c r="E51" t="n">
         <v>0.3287</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0498</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5365</v>
+        <v>-0.4781</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1405</v>
@@ -2848,7 +2848,7 @@
         <v>-0.06560000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.4961</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1849</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0663</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5537</v>
+        <v>-0.4969</v>
       </c>
       <c r="E54" t="n">
         <v>-0.1869</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0809</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.569</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2282</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1115</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6009</v>
+        <v>-0.5485</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3146</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1137</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6032</v>
+        <v>-0.551</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3208</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1269</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.617</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="E58" t="n">
         <v>-0.358</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1383</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6288</v>
+        <v>-0.5789</v>
       </c>
       <c r="E59" t="n">
         <v>-0.39</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1439</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6347</v>
+        <v>-0.5853</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4058</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1747</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6669</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4929</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1887</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6815</v>
+        <v>-0.6364</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5323</v>
@@ -3308,7 +3308,7 @@
         <v>-0.1898</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6826</v>
+        <v>-0.6377</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5354</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2324</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.727</v>
+        <v>-0.6861</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6554</v>
@@ -3400,7 +3400,7 @@
         <v>-0.2878</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7849</v>
+        <v>-0.7494</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8119</v>
@@ -3446,7 +3446,7 @@
         <v>-0.2927</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.79</v>
+        <v>-0.7549</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8256</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3173</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8157</v>
+        <v>-0.7829</v>
       </c>
       <c r="E67" t="n">
         <v>-0.895</v>
@@ -3538,7 +3538,7 @@
         <v>-0.3308</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8298</v>
+        <v>-0.7983</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9331</v>
@@ -3584,7 +3584,7 @@
         <v>-0.3343</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8334</v>
+        <v>-0.8023</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9429999999999999</v>
@@ -3630,7 +3630,7 @@
         <v>-0.3821</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8833</v>
+        <v>-0.8567</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0777</v>
@@ -3676,7 +3676,7 @@
         <v>-0.478</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.9661</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3484</v>
@@ -3722,7 +3722,7 @@
         <v>-0.4813</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9868</v>
+        <v>-0.9698</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3576</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5334</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0412</v>
+        <v>-1.0291</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5045</v>
@@ -3814,7 +3814,7 @@
         <v>-0.5874</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0976</v>
+        <v>-1.0907</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6569</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6126</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1239</v>
+        <v>-1.1194</v>
       </c>
       <c r="E75" t="n">
         <v>-1.728</v>
@@ -3906,7 +3906,7 @@
         <v>-0.6736</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1875</v>
+        <v>-1.1889</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8999</v>
@@ -3952,7 +3952,7 @@
         <v>-0.6872</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2017</v>
+        <v>-1.2044</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9383</v>
@@ -3998,7 +3998,7 @@
         <v>-0.7248</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2409</v>
+        <v>-1.2473</v>
       </c>
       <c r="E78" t="n">
         <v>-2.0444</v>
@@ -4044,7 +4044,7 @@
         <v>-0.7879</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3068</v>
+        <v>-1.3191</v>
       </c>
       <c r="E79" t="n">
         <v>-2.2223</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0313</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5608</v>
+        <v>-1.5965</v>
       </c>
       <c r="E80" t="n">
         <v>-2.9089</v>
@@ -4136,7 +4136,7 @@
         <v>-2.1587</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.7375</v>
+        <v>-2.8812</v>
       </c>
       <c r="E81" t="n">
         <v>-6.089</v>

--- a/database/event/8049/event_8049_evp_summary.xlsx
+++ b/database/event/8049/event_8049_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.0969</v>
       </c>
       <c r="D2" t="n">
-        <v>4.247</v>
+        <v>4.16</v>
       </c>
       <c r="E2" t="n">
         <v>11.5559</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.5916</v>
+        <v>8.5783</v>
       </c>
       <c r="C3" t="n">
-        <v>3.046</v>
+        <v>3.0413</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0495</v>
+        <v>2.9737</v>
       </c>
       <c r="E3" t="n">
-        <v>8.5916</v>
+        <v>8.5783</v>
       </c>
       <c r="F3" t="n">
-        <v>5.0553</v>
+        <v>5.0419</v>
       </c>
       <c r="G3" t="n">
         <v>3.5364</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6236</v>
+        <v>5.6026</v>
       </c>
       <c r="I3" t="n">
         <v>5.6498</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.1828</v>
+        <v>8.1655</v>
       </c>
       <c r="C4" t="n">
-        <v>2.9011</v>
+        <v>2.8949</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8843</v>
+        <v>2.8092</v>
       </c>
       <c r="E4" t="n">
-        <v>8.1828</v>
+        <v>8.1655</v>
       </c>
       <c r="F4" t="n">
-        <v>6.0975</v>
+        <v>6.0803</v>
       </c>
       <c r="G4" t="n">
         <v>2.0852</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2579</v>
+        <v>7.2308</v>
       </c>
       <c r="I4" t="n">
         <v>7.2916</v>
@@ -640,7 +640,7 @@
         <v>2.7859</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7531</v>
+        <v>2.6867</v>
       </c>
       <c r="E5" t="n">
         <v>7.8579</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.5728</v>
+        <v>7.5591</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6848</v>
+        <v>2.6799</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6379</v>
+        <v>2.5676</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5728</v>
+        <v>7.5591</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6808</v>
+        <v>3.6671</v>
       </c>
       <c r="G6" t="n">
         <v>3.892</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6808</v>
+        <v>3.6671</v>
       </c>
       <c r="I6" t="n">
         <v>3.698</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.2734</v>
+        <v>6.2584</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2241</v>
+        <v>2.2188</v>
       </c>
       <c r="D7" t="n">
-        <v>2.113</v>
+        <v>2.0494</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2734</v>
+        <v>6.2584</v>
       </c>
       <c r="F7" t="n">
-        <v>5.4981</v>
+        <v>5.4831</v>
       </c>
       <c r="G7" t="n">
         <v>0.7753</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3179</v>
+        <v>6.2943</v>
       </c>
       <c r="I7" t="n">
         <v>6.3473</v>
@@ -778,7 +778,7 @@
         <v>1.8948</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7377</v>
+        <v>1.6853</v>
       </c>
       <c r="E8" t="n">
         <v>5.3444</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.1455</v>
+        <v>5.1323</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8242</v>
+        <v>1.8196</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6573</v>
+        <v>1.6008</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1455</v>
+        <v>5.1323</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5501</v>
+        <v>3.5368</v>
       </c>
       <c r="G9" t="n">
         <v>1.5954</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5501</v>
+        <v>3.5368</v>
       </c>
       <c r="I9" t="n">
         <v>3.5666</v>
@@ -870,7 +870,7 @@
         <v>1.8143</v>
       </c>
       <c r="D10" t="n">
-        <v>1.646</v>
+        <v>1.5949</v>
       </c>
       <c r="E10" t="n">
         <v>5.1175</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.1125</v>
+        <v>5.1005</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8125</v>
+        <v>1.8083</v>
       </c>
       <c r="D11" t="n">
-        <v>1.644</v>
+        <v>1.5881</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1125</v>
+        <v>5.1005</v>
       </c>
       <c r="F11" t="n">
-        <v>4.671</v>
+        <v>4.659</v>
       </c>
       <c r="G11" t="n">
         <v>0.4415</v>
       </c>
       <c r="H11" t="n">
-        <v>5.021</v>
+        <v>5.0023</v>
       </c>
       <c r="I11" t="n">
         <v>5.0444</v>
@@ -962,7 +962,7 @@
         <v>1.5896</v>
       </c>
       <c r="D12" t="n">
-        <v>1.39</v>
+        <v>1.3424</v>
       </c>
       <c r="E12" t="n">
         <v>4.4837</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.2866</v>
+        <v>4.2726</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5197</v>
+        <v>1.5148</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3103</v>
+        <v>1.2583</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2866</v>
+        <v>4.2726</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7511</v>
+        <v>3.7371</v>
       </c>
       <c r="G13" t="n">
         <v>0.5355</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7511</v>
+        <v>3.7371</v>
       </c>
       <c r="I13" t="n">
         <v>3.7686</v>
@@ -1054,7 +1054,7 @@
         <v>1.3874</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1596</v>
+        <v>1.1152</v>
       </c>
       <c r="E14" t="n">
         <v>3.9134</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.57</v>
+        <v>3.5594</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2657</v>
+        <v>1.2619</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0208</v>
+        <v>0.9742</v>
       </c>
       <c r="E15" t="n">
-        <v>3.57</v>
+        <v>3.5594</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8228</v>
+        <v>2.8122</v>
       </c>
       <c r="G15" t="n">
         <v>0.7472</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8228</v>
+        <v>2.8122</v>
       </c>
       <c r="I15" t="n">
         <v>2.8359</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.5444</v>
+        <v>3.533</v>
       </c>
       <c r="C16" t="n">
-        <v>1.2566</v>
+        <v>1.2526</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0105</v>
+        <v>0.9636</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5444</v>
+        <v>3.533</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0439</v>
+        <v>3.0325</v>
       </c>
       <c r="G16" t="n">
         <v>0.5004999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0439</v>
+        <v>3.0325</v>
       </c>
       <c r="I16" t="n">
         <v>3.0581</v>
@@ -1192,7 +1192,7 @@
         <v>1.2271</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9769</v>
+        <v>0.9351</v>
       </c>
       <c r="E17" t="n">
         <v>3.4613</v>
@@ -1238,7 +1238,7 @@
         <v>1.1369</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8741</v>
+        <v>0.8337</v>
       </c>
       <c r="E18" t="n">
         <v>3.2068</v>
@@ -1284,7 +1284,7 @@
         <v>0.9409</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6508</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>2.6539</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6205</v>
+        <v>2.6078</v>
       </c>
       <c r="C20" t="n">
-        <v>0.929</v>
+        <v>0.9245</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6373</v>
+        <v>0.595</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6205</v>
+        <v>2.6078</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4032</v>
+        <v>3.3905</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7827</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4032</v>
+        <v>3.3905</v>
       </c>
       <c r="I20" t="n">
         <v>3.419</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5874</v>
+        <v>2.5775</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9173</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6239</v>
+        <v>0.583</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5874</v>
+        <v>2.5775</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6497</v>
+        <v>2.6398</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0623</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6497</v>
+        <v>2.6398</v>
       </c>
       <c r="I21" t="n">
         <v>2.662</v>
@@ -1422,7 +1422,7 @@
         <v>0.8206</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4782</v>
       </c>
       <c r="E22" t="n">
         <v>2.3145</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.2045</v>
+        <v>2.1925</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7816</v>
+        <v>0.7773</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4692</v>
+        <v>0.4296</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2045</v>
+        <v>2.1925</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2045</v>
+        <v>3.1925</v>
       </c>
       <c r="G23" t="n">
         <v>-1</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2045</v>
+        <v>3.1925</v>
       </c>
       <c r="I23" t="n">
         <v>3.2194</v>
@@ -1514,7 +1514,7 @@
         <v>0.7517</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4352</v>
+        <v>0.4009</v>
       </c>
       <c r="E24" t="n">
         <v>2.1204</v>
@@ -1560,7 +1560,7 @@
         <v>0.7127</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3908</v>
+        <v>0.357</v>
       </c>
       <c r="E25" t="n">
         <v>2.0104</v>
@@ -1606,7 +1606,7 @@
         <v>0.6932</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3685</v>
+        <v>0.335</v>
       </c>
       <c r="E26" t="n">
         <v>1.9552</v>
@@ -1652,7 +1652,7 @@
         <v>0.68</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3534</v>
+        <v>0.3202</v>
       </c>
       <c r="E27" t="n">
         <v>1.9179</v>
@@ -1698,7 +1698,7 @@
         <v>0.6718</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3441</v>
+        <v>0.311</v>
       </c>
       <c r="E28" t="n">
         <v>1.8949</v>
@@ -1744,7 +1744,7 @@
         <v>0.6667</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3383</v>
+        <v>0.3053</v>
       </c>
       <c r="E29" t="n">
         <v>1.8805</v>
@@ -1790,7 +1790,7 @@
         <v>0.6637999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.335</v>
+        <v>0.3021</v>
       </c>
       <c r="E30" t="n">
         <v>1.8724</v>
@@ -1836,7 +1836,7 @@
         <v>0.654</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3239</v>
+        <v>0.2911</v>
       </c>
       <c r="E31" t="n">
         <v>1.8448</v>
@@ -1882,7 +1882,7 @@
         <v>0.6512</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3207</v>
+        <v>0.2879</v>
       </c>
       <c r="E32" t="n">
         <v>1.8369</v>
@@ -1928,7 +1928,7 @@
         <v>0.6228</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2883</v>
+        <v>0.2559</v>
       </c>
       <c r="E33" t="n">
         <v>1.7566</v>
@@ -1974,7 +1974,7 @@
         <v>0.5985</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2606</v>
+        <v>0.2286</v>
       </c>
       <c r="E34" t="n">
         <v>1.6881</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.6079</v>
+        <v>1.5988</v>
       </c>
       <c r="C35" t="n">
-        <v>0.57</v>
+        <v>0.5668</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2282</v>
+        <v>0.1931</v>
       </c>
       <c r="E35" t="n">
-        <v>1.6079</v>
+        <v>1.5988</v>
       </c>
       <c r="F35" t="n">
-        <v>2.4476</v>
+        <v>2.4385</v>
       </c>
       <c r="G35" t="n">
         <v>-0.8397</v>
       </c>
       <c r="H35" t="n">
-        <v>2.4476</v>
+        <v>2.4385</v>
       </c>
       <c r="I35" t="n">
         <v>2.459</v>
@@ -2066,7 +2066,7 @@
         <v>0.5628</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2199</v>
+        <v>0.1885</v>
       </c>
       <c r="E36" t="n">
         <v>1.5874</v>
@@ -2112,7 +2112,7 @@
         <v>0.5518999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2076</v>
+        <v>0.1763</v>
       </c>
       <c r="E37" t="n">
         <v>1.5568</v>
@@ -2158,7 +2158,7 @@
         <v>0.5441</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1986</v>
+        <v>0.1675</v>
       </c>
       <c r="E38" t="n">
         <v>1.5347</v>
@@ -2204,7 +2204,7 @@
         <v>0.532</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1848</v>
+        <v>0.1539</v>
       </c>
       <c r="E39" t="n">
         <v>1.5005</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.3403</v>
+        <v>1.3329</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4752</v>
+        <v>0.4726</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1201</v>
+        <v>0.0871</v>
       </c>
       <c r="E40" t="n">
-        <v>1.3403</v>
+        <v>1.3329</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9619</v>
+        <v>1.9545</v>
       </c>
       <c r="G40" t="n">
         <v>-0.6216</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9619</v>
+        <v>1.9545</v>
       </c>
       <c r="I40" t="n">
         <v>1.971</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.2641</v>
+        <v>1.2578</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4482</v>
+        <v>0.4459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0893</v>
+        <v>0.0572</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2641</v>
+        <v>1.2578</v>
       </c>
       <c r="F41" t="n">
-        <v>1.6791</v>
+        <v>1.6728</v>
       </c>
       <c r="G41" t="n">
         <v>-0.415</v>
       </c>
       <c r="H41" t="n">
-        <v>1.6791</v>
+        <v>1.6728</v>
       </c>
       <c r="I41" t="n">
         <v>1.6869</v>
@@ -2342,7 +2342,7 @@
         <v>0.4064</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0417</v>
+        <v>0.0127</v>
       </c>
       <c r="E42" t="n">
         <v>1.1462</v>
@@ -2388,7 +2388,7 @@
         <v>0.3819</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0138</v>
+        <v>-0.0148</v>
       </c>
       <c r="E43" t="n">
         <v>1.0771</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.92</v>
+        <v>0.9179</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3262</v>
+        <v>0.3254</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0497</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>0.92</v>
+        <v>0.9179</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5599</v>
       </c>
       <c r="G44" t="n">
         <v>0.358</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5599</v>
       </c>
       <c r="I44" t="n">
         <v>0.5646</v>
@@ -2480,7 +2480,7 @@
         <v>0.2831</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0988</v>
+        <v>-0.1258</v>
       </c>
       <c r="E45" t="n">
         <v>0.7985</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7966</v>
+        <v>0.7914</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2824</v>
+        <v>0.2806</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1286</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7966</v>
+        <v>0.7914</v>
       </c>
       <c r="F46" t="n">
-        <v>1.401</v>
+        <v>1.3958</v>
       </c>
       <c r="G46" t="n">
         <v>-0.6044</v>
       </c>
       <c r="H46" t="n">
-        <v>1.401</v>
+        <v>1.3958</v>
       </c>
       <c r="I46" t="n">
         <v>1.4075</v>
@@ -2572,7 +2572,7 @@
         <v>0.2635</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1212</v>
+        <v>-0.1479</v>
       </c>
       <c r="E47" t="n">
         <v>0.7431</v>
@@ -2618,7 +2618,7 @@
         <v>0.2202</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1705</v>
+        <v>-0.1965</v>
       </c>
       <c r="E48" t="n">
         <v>0.621</v>
@@ -2664,7 +2664,7 @@
         <v>0.2184</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1725</v>
+        <v>-0.1985</v>
       </c>
       <c r="E49" t="n">
         <v>0.616</v>
@@ -2710,7 +2710,7 @@
         <v>0.1924</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2022</v>
+        <v>-0.2277</v>
       </c>
       <c r="E50" t="n">
         <v>0.5426</v>
@@ -2756,7 +2756,7 @@
         <v>0.1165</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2886</v>
+        <v>-0.313</v>
       </c>
       <c r="E51" t="n">
         <v>0.3287</v>
@@ -2802,7 +2802,7 @@
         <v>-0.0498</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4781</v>
+        <v>-0.4999</v>
       </c>
       <c r="E52" t="n">
         <v>-0.1405</v>
@@ -2848,7 +2848,7 @@
         <v>-0.06560000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4961</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="E53" t="n">
         <v>-0.1849</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0663</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4969</v>
+        <v>-0.5184</v>
       </c>
       <c r="E54" t="n">
         <v>-0.1869</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0809</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2282</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1115</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5485</v>
+        <v>-0.5692</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3146</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1137</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.551</v>
+        <v>-0.5717</v>
       </c>
       <c r="E57" t="n">
         <v>-0.3208</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.358</v>
+        <v>-0.3497</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1269</v>
+        <v>-0.124</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.358</v>
+        <v>-0.3497</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.2164</v>
+        <v>-2.2081</v>
       </c>
       <c r="G58" t="n">
         <v>1.8584</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.2164</v>
+        <v>-2.2081</v>
       </c>
       <c r="I58" t="n">
         <v>-2.2267</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1383</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5789</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="E59" t="n">
         <v>-0.39</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1439</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5853</v>
+        <v>-0.6056</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4058</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1747</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.6403</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4929</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1887</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6364</v>
+        <v>-0.656</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5323</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.5354</v>
+        <v>-0.5356</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1898</v>
+        <v>-0.1899</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6377</v>
+        <v>-0.6573</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5354</v>
+        <v>-0.5356</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0472</v>
+        <v>0.047</v>
       </c>
       <c r="G63" t="n">
         <v>-0.5826</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0472</v>
+        <v>0.047</v>
       </c>
       <c r="I63" t="n">
         <v>0.0474</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2324</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6861</v>
+        <v>-0.705</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6554</v>
@@ -3400,7 +3400,7 @@
         <v>-0.2878</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7494</v>
+        <v>-0.7674</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8119</v>
@@ -3446,7 +3446,7 @@
         <v>-0.2927</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7549</v>
+        <v>-0.7728</v>
       </c>
       <c r="E66" t="n">
         <v>-0.8256</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3173</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7829</v>
+        <v>-0.8005</v>
       </c>
       <c r="E67" t="n">
         <v>-0.895</v>
@@ -3538,7 +3538,7 @@
         <v>-0.3308</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7983</v>
+        <v>-0.8157</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9331</v>
@@ -3584,7 +3584,7 @@
         <v>-0.3343</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8023</v>
+        <v>-0.8196</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9429999999999999</v>
@@ -3630,7 +3630,7 @@
         <v>-0.3821</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8567</v>
+        <v>-0.8733</v>
       </c>
       <c r="E70" t="n">
         <v>-1.0777</v>
@@ -3676,7 +3676,7 @@
         <v>-0.478</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9661</v>
+        <v>-0.9811</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3484</v>
@@ -3722,7 +3722,7 @@
         <v>-0.4813</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9698</v>
+        <v>-0.9848</v>
       </c>
       <c r="E72" t="n">
         <v>-1.3576</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5334</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0291</v>
+        <v>-1.0433</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5045</v>
@@ -3814,7 +3814,7 @@
         <v>-0.5874</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0907</v>
+        <v>-1.104</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6569</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6126</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1194</v>
+        <v>-1.1323</v>
       </c>
       <c r="E75" t="n">
         <v>-1.728</v>
@@ -3906,7 +3906,7 @@
         <v>-0.6736</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1889</v>
+        <v>-1.2008</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8999</v>
@@ -3952,7 +3952,7 @@
         <v>-0.6872</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2044</v>
+        <v>-1.2161</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9383</v>
@@ -3998,7 +3998,7 @@
         <v>-0.7248</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2473</v>
+        <v>-1.2584</v>
       </c>
       <c r="E78" t="n">
         <v>-2.0444</v>
@@ -4044,7 +4044,7 @@
         <v>-0.7879</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3191</v>
+        <v>-1.3293</v>
       </c>
       <c r="E79" t="n">
         <v>-2.2223</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0313</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5965</v>
+        <v>-1.6028</v>
       </c>
       <c r="E80" t="n">
         <v>-2.9089</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-6.089</v>
+        <v>-6.0719</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.1587</v>
+        <v>-2.1527</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.8812</v>
+        <v>-2.863</v>
       </c>
       <c r="E81" t="n">
-        <v>-6.089</v>
+        <v>-6.0719</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.5842</v>
+        <v>-4.5671</v>
       </c>
       <c r="G81" t="n">
         <v>-1.5048</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.5842</v>
+        <v>-4.5671</v>
       </c>
       <c r="I81" t="n">
         <v>-4.6055</v>

--- a/database/event/8049/event_8049_evp_summary.xlsx
+++ b/database/event/8049/event_8049_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.4592</v>
+        <v>11.9622</v>
       </c>
       <c r="C2" t="n">
-        <v>4.0626</v>
+        <v>4.241</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5923</v>
+        <v>4.7294</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4592</v>
+        <v>11.9622</v>
       </c>
       <c r="F2" t="n">
         <v>5.2684</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.049300000000001</v>
+        <v>8.3187</v>
       </c>
       <c r="C3" t="n">
-        <v>2.8537</v>
+        <v>2.9492</v>
       </c>
       <c r="D3" t="n">
-        <v>3.04</v>
+        <v>3.102</v>
       </c>
       <c r="E3" t="n">
-        <v>8.049300000000001</v>
+        <v>8.3187</v>
       </c>
       <c r="F3" t="n">
         <v>4.6261</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.0868</v>
+        <v>7.3381</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5125</v>
+        <v>2.6016</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6019</v>
+        <v>2.6639</v>
       </c>
       <c r="E4" t="n">
-        <v>7.0868</v>
+        <v>7.3381</v>
       </c>
       <c r="F4" t="n">
         <v>5.1591</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.8433</v>
+        <v>7.0879</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4262</v>
+        <v>2.5129</v>
       </c>
       <c r="D5" t="n">
-        <v>2.491</v>
+        <v>2.5522</v>
       </c>
       <c r="E5" t="n">
-        <v>6.8433</v>
+        <v>7.0879</v>
       </c>
       <c r="F5" t="n">
         <v>3.3164</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.7577</v>
+        <v>6.897</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3958</v>
+        <v>2.4452</v>
       </c>
       <c r="D6" t="n">
-        <v>2.452</v>
+        <v>2.4669</v>
       </c>
       <c r="E6" t="n">
-        <v>6.7577</v>
+        <v>6.897</v>
       </c>
       <c r="F6" t="n">
         <v>3.1661</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.2915</v>
+        <v>6.7088</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2305</v>
+        <v>2.3785</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2398</v>
+        <v>2.3829</v>
       </c>
       <c r="E7" t="n">
-        <v>6.2915</v>
+        <v>6.7088</v>
       </c>
       <c r="F7" t="n">
         <v>5.6192</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.6308</v>
+        <v>5.6356</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9963</v>
+        <v>1.998</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9391</v>
+        <v>1.9035</v>
       </c>
       <c r="E8" t="n">
-        <v>5.6308</v>
+        <v>5.6356</v>
       </c>
       <c r="F8" t="n">
         <v>1.1264</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>luchov</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.7608</v>
+        <v>4.8443</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6878</v>
+        <v>1.7175</v>
       </c>
       <c r="D9" t="n">
-        <v>1.543</v>
+        <v>1.55</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7608</v>
+        <v>4.8443</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2901</v>
+        <v>3.6533</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4707</v>
+        <v>0.7592</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4762</v>
+        <v>5.271</v>
       </c>
       <c r="I9" t="n">
-        <v>4.5915</v>
+        <v>5.271</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4707</v>
+        <v>0.7592</v>
       </c>
       <c r="K9" t="n">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="L9" t="n">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="M9" t="n">
-        <v>6.0622</v>
+        <v>6.0302</v>
       </c>
       <c r="N9" t="n">
-        <v>428</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.5524</v>
+        <v>4.8382</v>
       </c>
       <c r="C10" t="n">
-        <v>1.614</v>
+        <v>1.7153</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4481</v>
+        <v>1.5473</v>
       </c>
       <c r="E10" t="n">
-        <v>4.5524</v>
+        <v>4.8382</v>
       </c>
       <c r="F10" t="n">
         <v>3.9555</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.453</v>
+        <v>4.7681</v>
       </c>
       <c r="C11" t="n">
-        <v>1.5787</v>
+        <v>1.6904</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4029</v>
+        <v>1.516</v>
       </c>
       <c r="E11" t="n">
-        <v>4.453</v>
+        <v>4.7681</v>
       </c>
       <c r="F11" t="n">
-        <v>3.9956</v>
+        <v>3.2901</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4574</v>
+        <v>1.4707</v>
       </c>
       <c r="H11" t="n">
-        <v>6.0202</v>
+        <v>4.4762</v>
       </c>
       <c r="I11" t="n">
-        <v>6.1753</v>
+        <v>4.5915</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4574</v>
+        <v>1.4707</v>
       </c>
       <c r="K11" t="n">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="L11" t="n">
-        <v>43</v>
+        <v>209</v>
       </c>
       <c r="M11" t="n">
-        <v>6.6327</v>
+        <v>6.0622</v>
       </c>
       <c r="N11" t="n">
-        <v>299</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>luchov</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.4125</v>
+        <v>4.5139</v>
       </c>
       <c r="C12" t="n">
-        <v>1.5644</v>
+        <v>1.6003</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3845</v>
+        <v>1.4024</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4125</v>
+        <v>4.5139</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6533</v>
+        <v>3.9956</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7592</v>
+        <v>0.4574</v>
       </c>
       <c r="H12" t="n">
-        <v>5.271</v>
+        <v>6.0202</v>
       </c>
       <c r="I12" t="n">
-        <v>5.271</v>
+        <v>6.1753</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7592</v>
+        <v>0.4574</v>
       </c>
       <c r="K12" t="n">
-        <v>159</v>
+        <v>256</v>
       </c>
       <c r="L12" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
-        <v>6.0302</v>
+        <v>6.6327</v>
       </c>
       <c r="N12" t="n">
-        <v>220</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.2917</v>
+        <v>4.4588</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5215</v>
+        <v>1.5808</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3295</v>
+        <v>1.3778</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2917</v>
+        <v>4.4588</v>
       </c>
       <c r="F13" t="n">
         <v>3.5316</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9876</v>
+        <v>4.2617</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4137</v>
+        <v>1.5109</v>
       </c>
       <c r="D14" t="n">
-        <v>1.191</v>
+        <v>1.2898</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9876</v>
+        <v>4.2617</v>
       </c>
       <c r="F14" t="n">
         <v>3.3366</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.8013</v>
+        <v>3.9151</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3477</v>
+        <v>1.388</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1062</v>
+        <v>1.135</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8013</v>
+        <v>3.9151</v>
       </c>
       <c r="F15" t="n">
         <v>3.1908</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.6836</v>
+        <v>3.723</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3059</v>
+        <v>1.3199</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0526</v>
+        <v>1.0492</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6836</v>
+        <v>3.723</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9326</v>
+        <v>3.5097</v>
       </c>
       <c r="G16" t="n">
-        <v>0.751</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6937</v>
+        <v>4.9568</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7889</v>
+        <v>4.9568</v>
       </c>
       <c r="J16" t="n">
-        <v>0.751</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="L16" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5399</v>
+        <v>4.9568</v>
       </c>
       <c r="N16" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.5097</v>
+        <v>3.6505</v>
       </c>
       <c r="C17" t="n">
-        <v>1.2443</v>
+        <v>1.2942</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9735</v>
+        <v>1.0168</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5097</v>
+        <v>3.6505</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5097</v>
+        <v>2.9326</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.751</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9568</v>
+        <v>3.6937</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9568</v>
+        <v>3.7889</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.751</v>
       </c>
       <c r="K17" t="n">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>4.9568</v>
+        <v>4.5399</v>
       </c>
       <c r="N17" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2226</v>
+        <v>3.2834</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1425</v>
+        <v>1.1641</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8428</v>
+        <v>0.8528</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2226</v>
+        <v>3.2834</v>
       </c>
       <c r="F18" t="n">
         <v>3.5363</v>
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0754</v>
+        <v>3.2555</v>
       </c>
       <c r="C19" t="n">
-        <v>1.0903</v>
+        <v>1.1542</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7758</v>
+        <v>0.8403</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0754</v>
+        <v>3.2555</v>
       </c>
       <c r="F19" t="n">
         <v>3.0754</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9702</v>
+        <v>2.9518</v>
       </c>
       <c r="C20" t="n">
-        <v>1.053</v>
+        <v>1.0465</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7279</v>
+        <v>0.7047</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9702</v>
+        <v>2.9518</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9702</v>
+        <v>2.7509</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1936</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7758</v>
+        <v>3.296</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7758</v>
+        <v>3.3809</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.1936</v>
       </c>
       <c r="K20" t="n">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7758</v>
+        <v>3.5745</v>
       </c>
       <c r="N20" t="n">
-        <v>279</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9445</v>
+        <v>2.9504</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0439</v>
+        <v>1.046</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9445</v>
+        <v>2.9504</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7509</v>
+        <v>2.9702</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1936</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.296</v>
+        <v>3.7758</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3809</v>
+        <v>3.7758</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1936</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5745</v>
+        <v>3.7758</v>
       </c>
       <c r="N21" t="n">
-        <v>299</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.8537</v>
+        <v>2.8096</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0117</v>
+        <v>0.9961</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6412</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8537</v>
+        <v>2.8096</v>
       </c>
       <c r="F22" t="n">
         <v>2.7585</v>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.6986</v>
+        <v>2.7908</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9567</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6328</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6986</v>
+        <v>2.7908</v>
       </c>
       <c r="F23" t="n">
         <v>2.6986</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>Rainwaker</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6444</v>
+        <v>2.7398</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9375</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5796</v>
+        <v>0.61</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6444</v>
+        <v>2.7398</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5753</v>
+        <v>2.6327</v>
       </c>
       <c r="G24" t="n">
-        <v>0.06909999999999999</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9117</v>
+        <v>3.0373</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9117</v>
+        <v>3.0373</v>
       </c>
       <c r="J24" t="n">
-        <v>0.06909999999999999</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="L24" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9808</v>
+        <v>3.0373</v>
       </c>
       <c r="N24" t="n">
-        <v>278</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.6406</v>
+        <v>2.6628</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9362</v>
+        <v>0.944</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5779</v>
+        <v>0.5756</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6406</v>
+        <v>2.6628</v>
       </c>
       <c r="F25" t="n">
         <v>3.3881</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rainwaker</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6327</v>
+        <v>2.5936</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9334</v>
+        <v>0.9195</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5743</v>
+        <v>0.5447</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6327</v>
+        <v>2.5936</v>
       </c>
       <c r="F26" t="n">
-        <v>2.6327</v>
+        <v>2.5753</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>3.0373</v>
+        <v>2.9117</v>
       </c>
       <c r="I26" t="n">
-        <v>3.0373</v>
+        <v>2.9117</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.0373</v>
+        <v>2.9808</v>
       </c>
       <c r="N26" t="n">
-        <v>221</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27">
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.4938</v>
+        <v>2.5518</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8841</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.511</v>
+        <v>0.526</v>
       </c>
       <c r="E27" t="n">
-        <v>2.4938</v>
+        <v>2.5518</v>
       </c>
       <c r="F27" t="n">
         <v>2.4938</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>xiELO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4319</v>
+        <v>2.5185</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8622</v>
+        <v>0.8929</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4828</v>
+        <v>0.5111</v>
       </c>
       <c r="E28" t="n">
-        <v>2.4319</v>
+        <v>2.5185</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4319</v>
+        <v>2.3722</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.5977</v>
+        <v>2.467</v>
       </c>
       <c r="I28" t="n">
-        <v>2.5977</v>
+        <v>2.467</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5977</v>
+        <v>2.467</v>
       </c>
       <c r="N28" t="n">
-        <v>279</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.3967</v>
+        <v>2.5173</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8497</v>
+        <v>0.8925</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4668</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.3967</v>
+        <v>2.5173</v>
       </c>
       <c r="F29" t="n">
         <v>3.1446</v>
@@ -1780,231 +1780,231 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>xiELO</t>
+          <t>AW</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.3722</v>
+        <v>2.3983</v>
       </c>
       <c r="C30" t="n">
-        <v>0.841</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4557</v>
+        <v>0.4574</v>
       </c>
       <c r="E30" t="n">
-        <v>2.3722</v>
+        <v>2.3983</v>
       </c>
       <c r="F30" t="n">
-        <v>2.3722</v>
+        <v>0.8518</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.4849</v>
       </c>
       <c r="H30" t="n">
-        <v>2.467</v>
+        <v>0.8518</v>
       </c>
       <c r="I30" t="n">
-        <v>2.467</v>
+        <v>0.8518</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.4849</v>
       </c>
       <c r="K30" t="n">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M30" t="n">
-        <v>2.467</v>
+        <v>2.3367</v>
       </c>
       <c r="N30" t="n">
-        <v>193</v>
+        <v>410</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.3368</v>
+        <v>2.3782</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8285</v>
+        <v>0.8431</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4396</v>
+        <v>0.4485</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3368</v>
+        <v>2.3782</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8518</v>
+        <v>2.4319</v>
       </c>
       <c r="G31" t="n">
-        <v>1.4849</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8518</v>
+        <v>2.5977</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8518</v>
+        <v>2.5977</v>
       </c>
       <c r="J31" t="n">
-        <v>1.4849</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="L31" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.3367</v>
+        <v>2.5977</v>
       </c>
       <c r="N31" t="n">
-        <v>410</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.3285</v>
+        <v>2.3715</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8255</v>
+        <v>0.8408</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4358</v>
+        <v>0.4455</v>
       </c>
       <c r="E32" t="n">
-        <v>2.3285</v>
+        <v>2.3715</v>
       </c>
       <c r="F32" t="n">
-        <v>2.3285</v>
+        <v>2.3162</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.3714</v>
+        <v>2.3445</v>
       </c>
       <c r="I32" t="n">
-        <v>2.3714</v>
+        <v>2.3445</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>293</v>
+        <v>221</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.3714</v>
+        <v>2.3445</v>
       </c>
       <c r="N32" t="n">
-        <v>293</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.3162</v>
+        <v>2.3476</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8212</v>
+        <v>0.8323</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4302</v>
+        <v>0.4348</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3162</v>
+        <v>2.3476</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3162</v>
+        <v>2.0846</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.2289</v>
       </c>
       <c r="H33" t="n">
-        <v>2.3445</v>
+        <v>2.0846</v>
       </c>
       <c r="I33" t="n">
-        <v>2.3445</v>
+        <v>2.0846</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.2289</v>
       </c>
       <c r="K33" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M33" t="n">
-        <v>2.3445</v>
+        <v>2.3135</v>
       </c>
       <c r="N33" t="n">
-        <v>221</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.3135</v>
+        <v>2.3009</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8202</v>
+        <v>0.8157</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4289</v>
+        <v>0.4139</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3135</v>
+        <v>2.3009</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0846</v>
+        <v>2.3285</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2289</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.0846</v>
+        <v>2.3714</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0846</v>
+        <v>2.3714</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2289</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>233</v>
+        <v>293</v>
       </c>
       <c r="L34" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.3135</v>
+        <v>2.3714</v>
       </c>
       <c r="N34" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.3113</v>
+        <v>2.242</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8194</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4279</v>
+        <v>0.3876</v>
       </c>
       <c r="E35" t="n">
-        <v>2.3113</v>
+        <v>2.242</v>
       </c>
       <c r="F35" t="n">
         <v>2.9673</v>
@@ -2056,323 +2056,323 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.2574</v>
+        <v>2.2359</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8003</v>
+        <v>0.7927</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4034</v>
+        <v>0.3849</v>
       </c>
       <c r="E36" t="n">
-        <v>2.2574</v>
+        <v>2.2359</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0581</v>
+        <v>1.9696</v>
       </c>
       <c r="G36" t="n">
-        <v>2.1993</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0581</v>
+        <v>1.9696</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0581</v>
+        <v>1.9696</v>
       </c>
       <c r="J36" t="n">
-        <v>2.1993</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="L36" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.2574</v>
+        <v>1.9696</v>
       </c>
       <c r="N36" t="n">
-        <v>312</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>tenzy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.2151</v>
+        <v>2.1033</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7853</v>
+        <v>0.7457</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3842</v>
+        <v>0.3257</v>
       </c>
       <c r="E37" t="n">
-        <v>2.2151</v>
+        <v>2.1033</v>
       </c>
       <c r="F37" t="n">
-        <v>2.5902</v>
+        <v>1.8234</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3751</v>
+        <v>0.2305</v>
       </c>
       <c r="H37" t="n">
-        <v>2.9441</v>
+        <v>1.8234</v>
       </c>
       <c r="I37" t="n">
-        <v>2.9441</v>
+        <v>1.8234</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3751</v>
+        <v>0.2305</v>
       </c>
       <c r="K37" t="n">
-        <v>159</v>
+        <v>311</v>
       </c>
       <c r="L37" t="n">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="M37" t="n">
-        <v>2.569</v>
+        <v>2.0539</v>
       </c>
       <c r="N37" t="n">
-        <v>220</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tenzy</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.0539</v>
+        <v>2.0774</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7282</v>
+        <v>0.7365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3108</v>
+        <v>0.3141</v>
       </c>
       <c r="E38" t="n">
-        <v>2.0539</v>
+        <v>2.0774</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8234</v>
+        <v>0.0581</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2305</v>
+        <v>2.1993</v>
       </c>
       <c r="H38" t="n">
-        <v>1.8234</v>
+        <v>0.0581</v>
       </c>
       <c r="I38" t="n">
-        <v>1.8234</v>
+        <v>0.0581</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2305</v>
+        <v>2.1993</v>
       </c>
       <c r="K38" t="n">
-        <v>311</v>
+        <v>167</v>
       </c>
       <c r="L38" t="n">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="M38" t="n">
-        <v>2.0539</v>
+        <v>2.2574</v>
       </c>
       <c r="N38" t="n">
-        <v>410</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.9997</v>
+        <v>1.9771</v>
       </c>
       <c r="C39" t="n">
-        <v>0.709</v>
+        <v>0.7009</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2861</v>
+        <v>0.2693</v>
       </c>
       <c r="E39" t="n">
-        <v>1.9997</v>
+        <v>1.9771</v>
       </c>
       <c r="F39" t="n">
-        <v>2.092</v>
+        <v>2.5902</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.3751</v>
       </c>
       <c r="H39" t="n">
-        <v>2.092</v>
+        <v>2.9441</v>
       </c>
       <c r="I39" t="n">
-        <v>2.1459</v>
+        <v>2.9441</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.3751</v>
       </c>
       <c r="K39" t="n">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="L39" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="M39" t="n">
-        <v>2.0536</v>
+        <v>2.569</v>
       </c>
       <c r="N39" t="n">
-        <v>308</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>sk0R</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.9696</v>
+        <v>1.9655</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6983</v>
+        <v>0.6968</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2724</v>
+        <v>0.2641</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9696</v>
+        <v>1.9655</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9696</v>
+        <v>1.5921</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9696</v>
+        <v>1.5921</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9696</v>
+        <v>1.5921</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9696</v>
+        <v>1.5921</v>
       </c>
       <c r="N40" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>sausol</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.9079</v>
+        <v>1.9025</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6764</v>
+        <v>0.6745</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2443</v>
+        <v>0.236</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9079</v>
+        <v>1.9025</v>
       </c>
       <c r="F41" t="n">
-        <v>2.719</v>
+        <v>1.8315</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8111</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3.226</v>
+        <v>1.8315</v>
       </c>
       <c r="I41" t="n">
-        <v>3.3092</v>
+        <v>1.8315</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8111</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="L41" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.4981</v>
+        <v>1.8315</v>
       </c>
       <c r="N41" t="n">
-        <v>367</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sausol</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.8315</v>
+        <v>1.8833</v>
       </c>
       <c r="C42" t="n">
-        <v>0.6493</v>
+        <v>0.6677</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2095</v>
+        <v>0.2274</v>
       </c>
       <c r="E42" t="n">
-        <v>1.8315</v>
+        <v>1.8833</v>
       </c>
       <c r="F42" t="n">
-        <v>1.8315</v>
+        <v>2.719</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-0.8111</v>
       </c>
       <c r="H42" t="n">
-        <v>1.8315</v>
+        <v>3.226</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8315</v>
+        <v>3.3092</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-0.8111</v>
       </c>
       <c r="K42" t="n">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M42" t="n">
-        <v>1.8315</v>
+        <v>2.4981</v>
       </c>
       <c r="N42" t="n">
-        <v>279</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43">
@@ -2382,16 +2382,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.8207</v>
+        <v>1.8358</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6455</v>
+        <v>0.6508</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2046</v>
+        <v>0.2062</v>
       </c>
       <c r="E43" t="n">
-        <v>1.8207</v>
+        <v>1.8358</v>
       </c>
       <c r="F43" t="n">
         <v>1.8207</v>
@@ -2424,35 +2424,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.7354</v>
+        <v>1.8009</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6153</v>
+        <v>0.6385</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1658</v>
+        <v>0.1906</v>
       </c>
       <c r="E44" t="n">
-        <v>1.7354</v>
+        <v>1.8009</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3658</v>
+        <v>2.092</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3696</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>1.3658</v>
+        <v>2.092</v>
       </c>
       <c r="I44" t="n">
-        <v>1.401</v>
+        <v>2.1459</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3696</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="K44" t="n">
         <v>208</v>
@@ -2461,7 +2461,7 @@
         <v>100</v>
       </c>
       <c r="M44" t="n">
-        <v>1.7706</v>
+        <v>2.0536</v>
       </c>
       <c r="N44" t="n">
         <v>308</v>
@@ -2470,47 +2470,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.6607</v>
+        <v>1.5295</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5888</v>
+        <v>0.5423</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1318</v>
+        <v>0.0694</v>
       </c>
       <c r="E45" t="n">
-        <v>1.6607</v>
+        <v>1.5295</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1797</v>
+        <v>1.3658</v>
       </c>
       <c r="G45" t="n">
-        <v>1.8404</v>
+        <v>0.3696</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.1797</v>
+        <v>1.3658</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1797</v>
+        <v>1.401</v>
       </c>
       <c r="J45" t="n">
-        <v>1.8404</v>
+        <v>0.3696</v>
       </c>
       <c r="K45" t="n">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="L45" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="M45" t="n">
-        <v>1.6607</v>
+        <v>1.7706</v>
       </c>
       <c r="N45" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46">
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.6073</v>
+        <v>1.5206</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5698</v>
+        <v>0.5391</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1075</v>
+        <v>0.0654</v>
       </c>
       <c r="E46" t="n">
-        <v>1.6073</v>
+        <v>1.5206</v>
       </c>
       <c r="F46" t="n">
         <v>1.6073</v>
@@ -2562,185 +2562,185 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sk0R</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.5921</v>
+        <v>1.4873</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5644</v>
+        <v>0.5273</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1006</v>
+        <v>0.0505</v>
       </c>
       <c r="E47" t="n">
-        <v>1.5921</v>
+        <v>1.4873</v>
       </c>
       <c r="F47" t="n">
-        <v>1.5921</v>
+        <v>-0.1797</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1.8404</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5921</v>
+        <v>-0.1797</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5921</v>
+        <v>-0.1797</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1.8404</v>
       </c>
       <c r="K47" t="n">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="M47" t="n">
-        <v>1.5921</v>
+        <v>1.6607</v>
       </c>
       <c r="N47" t="n">
-        <v>174</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.5709</v>
+        <v>1.4129</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5569</v>
+        <v>0.5009</v>
       </c>
       <c r="D48" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0173</v>
       </c>
       <c r="E48" t="n">
-        <v>1.5709</v>
+        <v>1.4129</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5709</v>
+        <v>1.2533</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5709</v>
+        <v>1.2533</v>
       </c>
       <c r="I48" t="n">
-        <v>1.5709</v>
+        <v>1.2533</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>293</v>
+        <v>172</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.5709</v>
+        <v>1.2533</v>
       </c>
       <c r="N48" t="n">
-        <v>293</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.569</v>
+        <v>1.402</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5563</v>
+        <v>0.4971</v>
       </c>
       <c r="D49" t="n">
-        <v>0.09</v>
+        <v>0.0124</v>
       </c>
       <c r="E49" t="n">
-        <v>1.569</v>
+        <v>1.402</v>
       </c>
       <c r="F49" t="n">
-        <v>1.8588</v>
+        <v>1.5709</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.2898</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.8588</v>
+        <v>1.5709</v>
       </c>
       <c r="I49" t="n">
-        <v>1.9068</v>
+        <v>1.5709</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.2898</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L49" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1.617</v>
+        <v>1.5709</v>
       </c>
       <c r="N49" t="n">
-        <v>367</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.2533</v>
+        <v>1.3935</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4443</v>
+        <v>0.494</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.0537</v>
+        <v>0.0086</v>
       </c>
       <c r="E50" t="n">
-        <v>1.2533</v>
+        <v>1.3935</v>
       </c>
       <c r="F50" t="n">
-        <v>1.2533</v>
+        <v>1.8588</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.2898</v>
       </c>
       <c r="H50" t="n">
-        <v>1.2533</v>
+        <v>1.8588</v>
       </c>
       <c r="I50" t="n">
-        <v>1.2533</v>
+        <v>1.9068</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.2898</v>
       </c>
       <c r="K50" t="n">
-        <v>172</v>
+        <v>291</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M50" t="n">
-        <v>1.2533</v>
+        <v>1.617</v>
       </c>
       <c r="N50" t="n">
-        <v>172</v>
+        <v>367</v>
       </c>
     </row>
     <row r="51">
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.2074</v>
+        <v>1.1596</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4281</v>
+        <v>0.4111</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.0746</v>
+        <v>-0.0959</v>
       </c>
       <c r="E51" t="n">
-        <v>1.2074</v>
+        <v>1.1596</v>
       </c>
       <c r="F51" t="n">
         <v>0.2538</v>
@@ -2792,231 +2792,231 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sFade8</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8051</v>
+        <v>0.8117</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2854</v>
+        <v>0.2878</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2577</v>
+        <v>-0.2513</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8051</v>
+        <v>0.8117</v>
       </c>
       <c r="F52" t="n">
-        <v>2.4301</v>
+        <v>0.6464</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.625</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.5937</v>
+        <v>0.6464</v>
       </c>
       <c r="I52" t="n">
-        <v>2.5937</v>
+        <v>0.6464</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.625</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>311</v>
+        <v>175</v>
       </c>
       <c r="L52" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.9687000000000001</v>
+        <v>0.6464</v>
       </c>
       <c r="N52" t="n">
-        <v>410</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>sFade8</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6464</v>
+        <v>0.8022</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2292</v>
+        <v>0.2844</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3299</v>
+        <v>-0.2555</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6464</v>
+        <v>0.8022</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6464</v>
+        <v>2.4301</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-1.625</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6464</v>
+        <v>2.5937</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6464</v>
+        <v>2.5937</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-1.625</v>
       </c>
       <c r="K53" t="n">
-        <v>175</v>
+        <v>311</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M53" t="n">
-        <v>0.6464</v>
+        <v>0.9687000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>175</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>mo0N</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5607</v>
+        <v>0.4926</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1988</v>
+        <v>0.1746</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.369</v>
+        <v>-0.3938</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5607</v>
+        <v>0.4926</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6456</v>
+        <v>0.4163</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.0849</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6456</v>
+        <v>0.4163</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6456</v>
+        <v>0.4163</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.0849</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>311</v>
+        <v>221</v>
       </c>
       <c r="L54" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5607</v>
+        <v>0.4163</v>
       </c>
       <c r="N54" t="n">
-        <v>410</v>
+        <v>221</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>mo0N</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4286</v>
+        <v>0.4564</v>
       </c>
       <c r="C55" t="n">
-        <v>0.152</v>
+        <v>0.1618</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4291</v>
+        <v>-0.41</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4286</v>
+        <v>0.4564</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4286</v>
+        <v>0.6456</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.0849</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4286</v>
+        <v>0.6456</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4286</v>
+        <v>0.6456</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.0849</v>
       </c>
       <c r="K55" t="n">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4286</v>
+        <v>0.5607</v>
       </c>
       <c r="N55" t="n">
-        <v>193</v>
+        <v>410</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>nota</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4163</v>
+        <v>0.3008</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1476</v>
+        <v>0.1066</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4347</v>
+        <v>-0.4795</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4163</v>
+        <v>0.3008</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4163</v>
+        <v>0.4286</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4163</v>
+        <v>0.4286</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4163</v>
+        <v>0.4286</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4163</v>
+        <v>0.4286</v>
       </c>
       <c r="N56" t="n">
-        <v>221</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57">
@@ -3026,16 +3026,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3296</v>
+        <v>0.2205</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1169</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4742</v>
+        <v>-0.5153</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3296</v>
+        <v>0.2205</v>
       </c>
       <c r="F57" t="n">
         <v>-1.365</v>
@@ -3068,277 +3068,277 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3227</v>
+        <v>0.2154</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1144</v>
+        <v>0.0764</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4773</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3227</v>
+        <v>0.2154</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4776</v>
+        <v>0.2987</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.1549</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4776</v>
+        <v>0.2987</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4776</v>
+        <v>0.2987</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.1549</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>233</v>
+        <v>293</v>
       </c>
       <c r="L58" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.3227</v>
+        <v>0.2987</v>
       </c>
       <c r="N58" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>BELCHONOKK</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2987</v>
+        <v>0.0534</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1059</v>
+        <v>0.0189</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4882</v>
+        <v>-0.59</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2987</v>
+        <v>0.0534</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2987</v>
+        <v>0.2609</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2987</v>
+        <v>0.2609</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2987</v>
+        <v>0.2609</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>293</v>
+        <v>193</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.2987</v>
+        <v>0.2609</v>
       </c>
       <c r="N59" t="n">
-        <v>293</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BELCHONOKK</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2609</v>
+        <v>0.0481</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0925</v>
+        <v>0.0171</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5054</v>
+        <v>-0.5923</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2609</v>
+        <v>0.0481</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2609</v>
+        <v>0.7309</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-0.6367</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2609</v>
+        <v>0.7309</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2609</v>
+        <v>0.7497</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-0.6367</v>
       </c>
       <c r="K60" t="n">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M60" t="n">
-        <v>0.2609</v>
+        <v>0.113</v>
       </c>
       <c r="N60" t="n">
-        <v>193</v>
+        <v>367</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0269</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0334</v>
+        <v>0.0095</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5813</v>
+        <v>-0.6018</v>
       </c>
       <c r="E61" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0269</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7309</v>
+        <v>0.4776</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.6367</v>
+        <v>-0.1549</v>
       </c>
       <c r="H61" t="n">
-        <v>0.7309</v>
+        <v>0.4776</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7497</v>
+        <v>0.4776</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.6367</v>
+        <v>-0.1549</v>
       </c>
       <c r="K61" t="n">
-        <v>291</v>
+        <v>233</v>
       </c>
       <c r="L61" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="M61" t="n">
-        <v>0.113</v>
+        <v>0.3227</v>
       </c>
       <c r="N61" t="n">
-        <v>367</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>xeedo</t>
+          <t>meyern</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0013</v>
+        <v>0.002</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6248</v>
+        <v>-0.6129</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0013</v>
+        <v>0.002</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0013</v>
+        <v>-1.2638</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1.2607</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.0013</v>
+        <v>-1.2638</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0013</v>
+        <v>-1.2638</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1.2607</v>
       </c>
       <c r="K62" t="n">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.0013</v>
+        <v>-0.003100000000000103</v>
       </c>
       <c r="N62" t="n">
-        <v>172</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>meyern</t>
+          <t>xeedo</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.0031</v>
+        <v>-0.1003</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0011</v>
+        <v>-0.0356</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6256</v>
+        <v>-0.6586</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.0031</v>
+        <v>-0.1003</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.2638</v>
+        <v>-0.0013</v>
       </c>
       <c r="G63" t="n">
-        <v>1.2607</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.2638</v>
+        <v>-0.0013</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.2638</v>
+        <v>-0.0013</v>
       </c>
       <c r="J63" t="n">
-        <v>1.2607</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="L63" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.003100000000000103</v>
+        <v>-0.0013</v>
       </c>
       <c r="N63" t="n">
-        <v>220</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.0389</v>
+        <v>-0.2642</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0138</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6419</v>
+        <v>-0.7318</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0389</v>
+        <v>-0.2642</v>
       </c>
       <c r="F64" t="n">
         <v>-0.0389</v>
@@ -3390,124 +3390,124 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>xerolte</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2547</v>
+        <v>-0.2963</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.105</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7401</v>
+        <v>-0.7462</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2547</v>
+        <v>-0.2963</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2547</v>
+        <v>-0.3253</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2547</v>
+        <v>-0.3253</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2547</v>
+        <v>-0.3253</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2547</v>
+        <v>-0.3253</v>
       </c>
       <c r="N65" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nin9</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3172</v>
+        <v>-0.3171</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1125</v>
+        <v>-0.1124</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3172</v>
+        <v>-0.3171</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.3172</v>
+        <v>-0.2547</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.3172</v>
+        <v>-0.2547</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3172</v>
+        <v>-0.2547</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3172</v>
+        <v>-0.2547</v>
       </c>
       <c r="N66" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>xerolte</t>
+          <t>nin9</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3253</v>
+        <v>-0.3543</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1153</v>
+        <v>-0.1256</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7723</v>
+        <v>-0.7721</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3253</v>
+        <v>-0.3543</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.3253</v>
+        <v>-0.3172</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.3253</v>
+        <v>-0.3172</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.3253</v>
+        <v>-0.3172</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.3253</v>
+        <v>-0.3172</v>
       </c>
       <c r="N67" t="n">
         <v>174</v>
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3312</v>
+        <v>-0.4613</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1174</v>
+        <v>-0.1635</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.775</v>
+        <v>-0.8199</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3312</v>
+        <v>-0.4613</v>
       </c>
       <c r="F68" t="n">
         <v>-0.3312</v>
@@ -3578,16 +3578,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4093</v>
+        <v>-0.5405</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1451</v>
+        <v>-0.1916</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8105</v>
+        <v>-0.8552</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4093</v>
+        <v>-0.5405</v>
       </c>
       <c r="F69" t="n">
         <v>-0.4093</v>
@@ -3620,32 +3620,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>corn</t>
+          <t>neaLaN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6518</v>
+        <v>-0.6683</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2311</v>
+        <v>-0.2369</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9209000000000001</v>
+        <v>-0.9123</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6518</v>
+        <v>-0.6683</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6518</v>
+        <v>-0.9217</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6518</v>
+        <v>-0.9217</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6518</v>
+        <v>-0.9217</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6518</v>
+        <v>-0.9217</v>
       </c>
       <c r="N70" t="n">
         <v>105</v>
@@ -3666,32 +3666,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>neaLaN</t>
+          <t>TH0R</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9217</v>
+        <v>-0.8514</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3268</v>
+        <v>-0.3018</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0438</v>
+        <v>-0.9941</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9217</v>
+        <v>-0.8514</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9217</v>
+        <v>-1.1461</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9217</v>
+        <v>-1.1461</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9217</v>
+        <v>-1.1461</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9217</v>
+        <v>-1.1461</v>
       </c>
       <c r="N71" t="n">
         <v>105</v>
@@ -3712,93 +3712,93 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AZUWU</t>
+          <t>corn</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9404</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3334</v>
+        <v>-0.3504</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0523</v>
+        <v>-1.0553</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9404</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9404</v>
+        <v>-0.6518</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9404</v>
+        <v>-0.6518</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9404</v>
+        <v>-0.6518</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9404</v>
+        <v>-0.6518</v>
       </c>
       <c r="N72" t="n">
-        <v>221</v>
+        <v>105</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>X5G7V</t>
+          <t>AZUWU</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1099</v>
+        <v>-1.0901</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.3935</v>
+        <v>-0.3865</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1295</v>
+        <v>-1.1007</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1099</v>
+        <v>-1.0901</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.1099</v>
+        <v>-0.9404</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.1099</v>
+        <v>-0.9404</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1099</v>
+        <v>-0.9404</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>172</v>
+        <v>221</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1099</v>
+        <v>-0.9404</v>
       </c>
       <c r="N73" t="n">
-        <v>172</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74">
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1114</v>
+        <v>-1.3487</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.394</v>
+        <v>-0.4782</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1301</v>
+        <v>-1.2163</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1114</v>
+        <v>-1.3487</v>
       </c>
       <c r="F74" t="n">
         <v>-1.1114</v>
@@ -3850,32 +3850,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TH0R</t>
+          <t>AlekS</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1461</v>
+        <v>-1.5466</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4063</v>
+        <v>-0.5483</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1459</v>
+        <v>-1.3047</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1461</v>
+        <v>-1.5466</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1461</v>
+        <v>-1.2612</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1461</v>
+        <v>-1.2612</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1461</v>
+        <v>-1.2612</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1461</v>
+        <v>-1.2612</v>
       </c>
       <c r="N75" t="n">
         <v>105</v>
@@ -3896,47 +3896,47 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AlekS</t>
+          <t>X5G7V</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.2612</v>
+        <v>-1.5816</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4471</v>
+        <v>-0.5607</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1983</v>
+        <v>-1.3203</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.2612</v>
+        <v>-1.5816</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.2612</v>
+        <v>-1.1099</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.2612</v>
+        <v>-1.1099</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2612</v>
+        <v>-1.1099</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.2612</v>
+        <v>-1.1099</v>
       </c>
       <c r="N76" t="n">
-        <v>105</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5504</v>
+        <v>-1.6728</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.5497</v>
+        <v>-0.5931</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.33</v>
+        <v>-1.361</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5504</v>
+        <v>-1.6728</v>
       </c>
       <c r="F77" t="n">
         <v>-1.5504</v>
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.6296</v>
+        <v>-1.8463</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5777</v>
+        <v>-0.6546</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.366</v>
+        <v>-1.4385</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.6296</v>
+        <v>-1.8463</v>
       </c>
       <c r="F78" t="n">
         <v>-1.6296</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.8846</v>
+        <v>-1.952</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6681</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4821</v>
+        <v>-1.4857</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.8846</v>
+        <v>-1.952</v>
       </c>
       <c r="F79" t="n">
         <v>-1.8846</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.1771</v>
+        <v>-2.5016</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7718</v>
+        <v>-0.8869</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6153</v>
+        <v>-1.7312</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.1771</v>
+        <v>-2.5016</v>
       </c>
       <c r="F80" t="n">
         <v>-2.1771</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-5.3563</v>
+        <v>-5.773</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.899</v>
+        <v>-2.0467</v>
       </c>
       <c r="D81" t="n">
-        <v>-3.0625</v>
+        <v>-3.1925</v>
       </c>
       <c r="E81" t="n">
-        <v>-5.3563</v>
+        <v>-5.773</v>
       </c>
       <c r="F81" t="n">
         <v>-3.8011</v>
